--- a/data/processed/positivacao/2020-08_positivacao_anonimizado.xlsx
+++ b/data/processed/positivacao/2020-08_positivacao_anonimizado.xlsx
@@ -551,7 +551,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Vendedor: 1 - ROBSON</t>
+          <t>Vendedor: 1 - VENDEDOR 01</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -23983,7 +23983,7 @@
     <row r="910">
       <c r="A910" t="inlineStr">
         <is>
-          <t>Vendedor: 3 - FERNANDA</t>
+          <t>Vendedor: 3 - VENDEDOR 03</t>
         </is>
       </c>
       <c r="B910" t="inlineStr"/>
@@ -35101,7 +35101,7 @@
     <row r="1338">
       <c r="A1338" t="inlineStr">
         <is>
-          <t>Vendedor: 4 - DANIELA</t>
+          <t>Vendedor: 4 - VENDEDOR 04</t>
         </is>
       </c>
       <c r="B1338" t="inlineStr"/>
@@ -64071,7 +64071,7 @@
     <row r="2453">
       <c r="A2453" t="inlineStr">
         <is>
-          <t>Vendedor: 8 - RAFAEL</t>
+          <t>Vendedor: 8 - VENDEDOR 08</t>
         </is>
       </c>
       <c r="B2453" t="inlineStr"/>
@@ -65742,12 +65742,12 @@
       <c r="A2518" t="inlineStr"/>
       <c r="B2518" t="inlineStr">
         <is>
-          <t>Vendedor 1 - ROBSON: positivou 0 cliente(s), não positivou 93 cliente(s) - Total vendido: R$ 0,00
+          <t>Vendedor 1 - VENDEDOR 01: positivou 0 cliente(s), não positivou 93 cliente(s) - Total vendido: R$ 0,00
 Vendedor 18 - LOJA: positivou 12 cliente(s), não positivou 795 cliente(s) - Total vendido: R$ 9.568,51
-Vendedor 3 - FERNANDA: positivou 1 cliente(s), não positivou 426 cliente(s) - Total vendido: R$ 353,90
-Vendedor 4 - DANIELA: positivou 0 cliente(s), não positivou 657 cliente(s) - Total vendido: R$ 0,00
+Vendedor 3 - VENDEDOR 03: positivou 1 cliente(s), não positivou 426 cliente(s) - Total vendido: R$ 353,90
+Vendedor 4 - VENDEDOR 04: positivou 0 cliente(s), não positivou 657 cliente(s) - Total vendido: R$ 0,00
 Vendedor 5 - SITE: positivou 1 cliente(s), não positivou 455 cliente(s) - Total vendido: R$ 124,90
-Vendedor 8 - RAFAEL: positivou 0 cliente(s), não positivou 63 cliente(s) - Total vendido: R$ 0,00</t>
+Vendedor 8 - VENDEDOR 08: positivou 0 cliente(s), não positivou 63 cliente(s) - Total vendido: R$ 0,00</t>
         </is>
       </c>
       <c r="C2518" t="inlineStr"/>
